--- a/department-course-clustering/data/raw/raw_source_register.xlsx
+++ b/department-course-clustering/data/raw/raw_source_register.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -747,6 +747,54 @@
       <c r="J6" t="inlineStr">
         <is>
           <t>대학/전형/모집단위별 내신 등급 컷. clustering feature가 아닌 해석 변수로만 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>internal_compiled</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>종합_교과_컷</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>종합_교과_컷.xlsx</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>내부 정리 자료</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>manual_excel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>admission score reference</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>전국 대학 교과/종합 전형의 대학발표 및 대학어디가 내신 컷. 기존 지거국 컷을 보강하는 해석 변수로 사용</t>
         </is>
       </c>
     </row>
